--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/10.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/10.xlsx
@@ -426,13 +426,13 @@
         <v>-19.1932458189947</v>
       </c>
       <c r="E2">
-        <v>-19.61466609284904</v>
+        <v>-18.7343171603359</v>
       </c>
       <c r="F2">
-        <v>-0.02684339293522573</v>
+        <v>-0.2398166521949786</v>
       </c>
       <c r="G2">
-        <v>-11.81897535664458</v>
+        <v>-8.66807407387633</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.01589718632047</v>
       </c>
       <c r="E3">
-        <v>-20.35211902805014</v>
+        <v>-18.72978868632823</v>
       </c>
       <c r="F3">
-        <v>-0.4566293943667072</v>
+        <v>-0.691724205118221</v>
       </c>
       <c r="G3">
-        <v>-12.1263897233274</v>
+        <v>-8.66103913485288</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.79752294252625</v>
       </c>
       <c r="E4">
-        <v>-20.24968041752263</v>
+        <v>-17.19065546907524</v>
       </c>
       <c r="F4">
-        <v>-0.313589396353497</v>
+        <v>-0.1461432095516049</v>
       </c>
       <c r="G4">
-        <v>-11.7162698406124</v>
+        <v>-7.218646949536577</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.54826228314219</v>
       </c>
       <c r="E5">
-        <v>-21.22591525867418</v>
+        <v>-18.67130344451917</v>
       </c>
       <c r="F5">
-        <v>-0.2511304941824143</v>
+        <v>-0.1106559500156741</v>
       </c>
       <c r="G5">
-        <v>-11.00715848695768</v>
+        <v>-9.532610330358823</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.28517698544071</v>
       </c>
       <c r="E6">
-        <v>-21.20351289775824</v>
+        <v>-19.00729810199228</v>
       </c>
       <c r="F6">
-        <v>-0.1086910625362337</v>
+        <v>-0.2173413878222224</v>
       </c>
       <c r="G6">
-        <v>-10.92992837511303</v>
+        <v>-8.198613299258776</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.01113797285822</v>
       </c>
       <c r="E7">
-        <v>-21.96250778381383</v>
+        <v>-19.69961120828492</v>
       </c>
       <c r="F7">
-        <v>-0.07301245013025617</v>
+        <v>-0.4712724449459941</v>
       </c>
       <c r="G7">
-        <v>-10.72148549432775</v>
+        <v>-7.871836444153677</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.73774400524497</v>
       </c>
       <c r="E8">
-        <v>-21.63699201519447</v>
+        <v>-21.69929023211799</v>
       </c>
       <c r="F8">
-        <v>0.2349604679847524</v>
+        <v>0.4831724765595963</v>
       </c>
       <c r="G8">
-        <v>-10.6081061645627</v>
+        <v>-7.918774318561534</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.46526165156562</v>
       </c>
       <c r="E9">
-        <v>-22.90232916546971</v>
+        <v>-22.60490804959393</v>
       </c>
       <c r="F9">
-        <v>-0.1588487087757438</v>
+        <v>-0.4700978199688244</v>
       </c>
       <c r="G9">
-        <v>-10.77254130179271</v>
+        <v>-8.458751825713113</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.18936737279208</v>
       </c>
       <c r="E10">
-        <v>-24.36952757311085</v>
+        <v>-21.39778896116131</v>
       </c>
       <c r="F10">
-        <v>0.2385547541454995</v>
+        <v>-0.02419096051146171</v>
       </c>
       <c r="G10">
-        <v>-10.48516863639498</v>
+        <v>-7.802281109536568</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.91323124879677</v>
       </c>
       <c r="E11">
-        <v>-23.6494005794631</v>
+        <v>-21.774861406358</v>
       </c>
       <c r="F11">
-        <v>0.3894998622836254</v>
+        <v>-0.121291359100217</v>
       </c>
       <c r="G11">
-        <v>-10.88740702492419</v>
+        <v>-8.835271999659394</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.62534827900289</v>
       </c>
       <c r="E12">
-        <v>-25.10909077719953</v>
+        <v>-24.17423260305607</v>
       </c>
       <c r="F12">
-        <v>0.5702073828369347</v>
+        <v>0.9854033492029085</v>
       </c>
       <c r="G12">
-        <v>-9.758630715038054</v>
+        <v>-8.819961819863025</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.31651147503476</v>
       </c>
       <c r="E13">
-        <v>-25.88038952713396</v>
+        <v>-23.82863305221268</v>
       </c>
       <c r="F13">
-        <v>1.019107962088015</v>
+        <v>0.9710593392560323</v>
       </c>
       <c r="G13">
-        <v>-9.818759100114878</v>
+        <v>-8.106322380456275</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.99546920833933</v>
       </c>
       <c r="E14">
-        <v>-26.16765780428454</v>
+        <v>-24.51990460948356</v>
       </c>
       <c r="F14">
-        <v>1.163575237136249</v>
+        <v>1.676868128076545</v>
       </c>
       <c r="G14">
-        <v>-9.868810853782648</v>
+        <v>-6.409110528833496</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.65867350808051</v>
       </c>
       <c r="E15">
-        <v>-26.77238116632082</v>
+        <v>-25.9891634727982</v>
       </c>
       <c r="F15">
-        <v>1.51682423238607</v>
+        <v>0.7459140493795434</v>
       </c>
       <c r="G15">
-        <v>-9.566502067846328</v>
+        <v>-7.189155330160288</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.31913328954163</v>
       </c>
       <c r="E16">
-        <v>-27.04658026748526</v>
+        <v>-25.73105856825703</v>
       </c>
       <c r="F16">
-        <v>1.384147938949284</v>
+        <v>1.78601713053902</v>
       </c>
       <c r="G16">
-        <v>-9.032627632795316</v>
+        <v>-7.099341733635168</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.984598682932</v>
       </c>
       <c r="E17">
-        <v>-28.36264085512041</v>
+        <v>-26.38868356365091</v>
       </c>
       <c r="F17">
-        <v>1.751537165764893</v>
+        <v>2.260825728680057</v>
       </c>
       <c r="G17">
-        <v>-8.678672419513335</v>
+        <v>-7.284294349276387</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.66264258953344</v>
       </c>
       <c r="E18">
-        <v>-29.53809685329141</v>
+        <v>-28.27801273286507</v>
       </c>
       <c r="F18">
-        <v>2.222498825687329</v>
+        <v>1.75570551053578</v>
       </c>
       <c r="G18">
-        <v>-8.472106397460053</v>
+        <v>-6.011331320403572</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.36898496237448</v>
       </c>
       <c r="E19">
-        <v>-29.56750929197123</v>
+        <v>-28.60966911223883</v>
       </c>
       <c r="F19">
-        <v>2.247003590196945</v>
+        <v>2.147799966772481</v>
       </c>
       <c r="G19">
-        <v>-7.838538607768433</v>
+        <v>-7.633813351009998</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.10281256119674</v>
       </c>
       <c r="E20">
-        <v>-31.19047814852822</v>
+        <v>-28.56488703277698</v>
       </c>
       <c r="F20">
-        <v>2.320761423742213</v>
+        <v>2.758706015723866</v>
       </c>
       <c r="G20">
-        <v>-7.278096121750597</v>
+        <v>-5.669063818316335</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.86066729063176</v>
       </c>
       <c r="E21">
-        <v>-31.49799096873009</v>
+        <v>-30.30422408590908</v>
       </c>
       <c r="F21">
-        <v>2.674442826776295</v>
+        <v>2.548774521567193</v>
       </c>
       <c r="G21">
-        <v>-7.969794032589339</v>
+        <v>-5.684908837226893</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.64678832569045</v>
       </c>
       <c r="E22">
-        <v>-32.59939283145366</v>
+        <v>-30.8257208883954</v>
       </c>
       <c r="F22">
-        <v>2.585790947328692</v>
+        <v>2.917475882348836</v>
       </c>
       <c r="G22">
-        <v>-7.762184582080154</v>
+        <v>-5.416199760059287</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.44967371935254</v>
       </c>
       <c r="E23">
-        <v>-32.51664176167449</v>
+        <v>-31.49424139225174</v>
       </c>
       <c r="F23">
-        <v>3.075387560344506</v>
+        <v>3.433495758779149</v>
       </c>
       <c r="G23">
-        <v>-7.051862457670002</v>
+        <v>-5.36418255467741</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.26779686480359</v>
       </c>
       <c r="E24">
-        <v>-33.53176260912991</v>
+        <v>-33.37031345380844</v>
       </c>
       <c r="F24">
-        <v>2.917146192122522</v>
+        <v>3.289778984597852</v>
       </c>
       <c r="G24">
-        <v>-6.825343327313736</v>
+        <v>-4.932865980688402</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.09247027623169</v>
       </c>
       <c r="E25">
-        <v>-34.23735772968705</v>
+        <v>-30.81552502916713</v>
       </c>
       <c r="F25">
-        <v>3.280294177835797</v>
+        <v>3.407827966436003</v>
       </c>
       <c r="G25">
-        <v>-6.44271023760221</v>
+        <v>-4.357382375042071</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.91632103631564</v>
       </c>
       <c r="E26">
-        <v>-34.2282985174347</v>
+        <v>-33.61317777907681</v>
       </c>
       <c r="F26">
-        <v>3.088782261247774</v>
+        <v>3.479466836164911</v>
       </c>
       <c r="G26">
-        <v>-5.819012362361399</v>
+        <v>-4.244800382115964</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.74297203612685</v>
       </c>
       <c r="E27">
-        <v>-34.51508904057747</v>
+        <v>-32.04863755840378</v>
       </c>
       <c r="F27">
-        <v>3.080906143981956</v>
+        <v>3.279706036979809</v>
       </c>
       <c r="G27">
-        <v>-6.461419762934163</v>
+        <v>-4.024249793776328</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.56618288932092</v>
       </c>
       <c r="E28">
-        <v>-34.3836274401348</v>
+        <v>-32.64201256457685</v>
       </c>
       <c r="F28">
-        <v>3.050872855426058</v>
+        <v>3.643003128825589</v>
       </c>
       <c r="G28">
-        <v>-6.112435600314742</v>
+        <v>-4.219836848491709</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.38403802211511</v>
       </c>
       <c r="E29">
-        <v>-35.51502591468517</v>
+        <v>-33.4525890338168</v>
       </c>
       <c r="F29">
-        <v>3.076224211421334</v>
+        <v>3.314338421356051</v>
       </c>
       <c r="G29">
-        <v>-5.697561227560112</v>
+        <v>-3.906417846355109</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.20296682343706</v>
       </c>
       <c r="E30">
-        <v>-33.24330107907831</v>
+        <v>-32.03776469231136</v>
       </c>
       <c r="F30">
-        <v>2.869253302362266</v>
+        <v>3.134302706766412</v>
       </c>
       <c r="G30">
-        <v>-6.439087769000583</v>
+        <v>-4.77912434452062</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.02015935841351</v>
       </c>
       <c r="E31">
-        <v>-34.57830880196155</v>
+        <v>-33.97745502096483</v>
       </c>
       <c r="F31">
-        <v>2.784781364829189</v>
+        <v>3.021412797112896</v>
       </c>
       <c r="G31">
-        <v>-5.331170184567837</v>
+        <v>-3.949434660999429</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.84299004719901</v>
       </c>
       <c r="E32">
-        <v>-34.68539589105794</v>
+        <v>-32.39576999769876</v>
       </c>
       <c r="F32">
-        <v>2.852470578781548</v>
+        <v>3.241316178064469</v>
       </c>
       <c r="G32">
-        <v>-5.309802869772732</v>
+        <v>-4.43178735512404</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.67118532523766</v>
       </c>
       <c r="E33">
-        <v>-34.4433195202669</v>
+        <v>-32.01735259572179</v>
       </c>
       <c r="F33">
-        <v>2.608198285574419</v>
+        <v>2.838780979082883</v>
       </c>
       <c r="G33">
-        <v>-5.722442730645382</v>
+        <v>-4.313473068133582</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.50633754408735</v>
       </c>
       <c r="E34">
-        <v>-33.69373706743626</v>
+        <v>-31.24267107570363</v>
       </c>
       <c r="F34">
-        <v>2.626882940711964</v>
+        <v>3.363278367513446</v>
       </c>
       <c r="G34">
-        <v>-6.209339916629824</v>
+        <v>-4.097381659893232</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.35764320565137</v>
       </c>
       <c r="E35">
-        <v>-33.6499535164931</v>
+        <v>-32.34887991358633</v>
       </c>
       <c r="F35">
-        <v>2.683639361682175</v>
+        <v>3.034812468220581</v>
       </c>
       <c r="G35">
-        <v>-5.655689559240038</v>
+        <v>-4.759522326924498</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.22357184148798</v>
       </c>
       <c r="E36">
-        <v>-33.00590715041121</v>
+        <v>-32.07211090342254</v>
       </c>
       <c r="F36">
-        <v>2.682814307748987</v>
+        <v>3.114135273977856</v>
       </c>
       <c r="G36">
-        <v>-4.971587676311409</v>
+        <v>-3.956239914513718</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.10659777668366</v>
       </c>
       <c r="E37">
-        <v>-33.58897082126881</v>
+        <v>-29.89992645497828</v>
       </c>
       <c r="F37">
-        <v>2.583940374550838</v>
+        <v>3.496203171171071</v>
       </c>
       <c r="G37">
-        <v>-4.859930987865065</v>
+        <v>-2.537213307922221</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.01223074026517</v>
       </c>
       <c r="E38">
-        <v>-32.57991133627265</v>
+        <v>-29.06582229903147</v>
       </c>
       <c r="F38">
-        <v>2.775082839277212</v>
+        <v>2.559215264312078</v>
       </c>
       <c r="G38">
-        <v>-5.800798301484921</v>
+        <v>-2.85642366611124</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.93848354297985</v>
       </c>
       <c r="E39">
-        <v>-32.76060424188972</v>
+        <v>-31.49785964298387</v>
       </c>
       <c r="F39">
-        <v>2.89227528922087</v>
+        <v>3.286089436185783</v>
       </c>
       <c r="G39">
-        <v>-5.542812256373581</v>
+        <v>-4.174158963162679</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.89038500454021</v>
       </c>
       <c r="E40">
-        <v>-31.31565422704825</v>
+        <v>-29.22387057037317</v>
       </c>
       <c r="F40">
-        <v>2.69648568336479</v>
+        <v>2.697933669584883</v>
       </c>
       <c r="G40">
-        <v>-5.57230387574987</v>
+        <v>-3.836796887306811</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.8630001861191</v>
       </c>
       <c r="E41">
-        <v>-32.50579380218912</v>
+        <v>-29.24910322754391</v>
       </c>
       <c r="F41">
-        <v>2.94366388942094</v>
+        <v>2.91487315196924</v>
       </c>
       <c r="G41">
-        <v>-4.540717348454486</v>
+        <v>-4.901609064113132</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.85382171780411</v>
       </c>
       <c r="E42">
-        <v>-31.49643770214546</v>
+        <v>-28.01281623802788</v>
       </c>
       <c r="F42">
-        <v>2.719736299626566</v>
+        <v>2.973364174280913</v>
       </c>
       <c r="G42">
-        <v>-5.157216223593875</v>
+        <v>-3.899428844433492</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.86498742324773</v>
       </c>
       <c r="E43">
-        <v>-30.43379731269055</v>
+        <v>-26.61400684485057</v>
       </c>
       <c r="F43">
-        <v>2.733357973198201</v>
+        <v>3.563763159808594</v>
       </c>
       <c r="G43">
-        <v>-5.408698887574396</v>
+        <v>-3.634739263676205</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.88816837524852</v>
       </c>
       <c r="E44">
-        <v>-30.9710192411685</v>
+        <v>-27.46921368967312</v>
       </c>
       <c r="F44">
-        <v>2.913660422091542</v>
+        <v>3.270880610670384</v>
       </c>
       <c r="G44">
-        <v>-5.291428029039842</v>
+        <v>-3.599413632367224</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.91975533213177</v>
       </c>
       <c r="E45">
-        <v>-30.52239690665062</v>
+        <v>-27.62321803372598</v>
       </c>
       <c r="F45">
-        <v>2.680040933684414</v>
+        <v>2.992519342103249</v>
       </c>
       <c r="G45">
-        <v>-5.450445869475212</v>
+        <v>-4.665042833341846</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.95601614822208</v>
       </c>
       <c r="E46">
-        <v>-29.77612250408258</v>
+        <v>-25.20401212087431</v>
       </c>
       <c r="F46">
-        <v>2.586183593477619</v>
+        <v>3.333728845520782</v>
       </c>
       <c r="G46">
-        <v>-5.36205632310689</v>
+        <v>-4.375573467367634</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.99182504079463</v>
       </c>
       <c r="E47">
-        <v>-29.75623344624089</v>
+        <v>-26.39178556834617</v>
       </c>
       <c r="F47">
-        <v>2.779981804097369</v>
+        <v>3.107664067827186</v>
       </c>
       <c r="G47">
-        <v>-5.154663433220628</v>
+        <v>-3.653097698301298</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.0300651400255</v>
       </c>
       <c r="E48">
-        <v>-28.25590925123363</v>
+        <v>-26.80630396511228</v>
       </c>
       <c r="F48">
-        <v>2.658944072669916</v>
+        <v>2.507134148963268</v>
       </c>
       <c r="G48">
-        <v>-5.771726678468241</v>
+        <v>-3.991276798325468</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.06444260335784</v>
       </c>
       <c r="E49">
-        <v>-28.78892875583247</v>
+        <v>-26.16885784989657</v>
       </c>
       <c r="F49">
-        <v>2.862217149642887</v>
+        <v>2.9976237420393</v>
       </c>
       <c r="G49">
-        <v>-5.50428743404414</v>
+        <v>-4.596140461815066</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.09365870318713</v>
       </c>
       <c r="E50">
-        <v>-27.61973563721408</v>
+        <v>-24.62605656869736</v>
       </c>
       <c r="F50">
-        <v>3.161961894345888</v>
+        <v>3.327181429569055</v>
       </c>
       <c r="G50">
-        <v>-5.702834150606139</v>
+        <v>-4.622150705116785</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.12171975378654</v>
       </c>
       <c r="E51">
-        <v>-27.25165674139662</v>
+        <v>-25.23285850030317</v>
       </c>
       <c r="F51">
-        <v>3.13700649796915</v>
+        <v>3.007991588452738</v>
       </c>
       <c r="G51">
-        <v>-6.115047452676061</v>
+        <v>-4.369519613590458</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.14445608563493</v>
       </c>
       <c r="E52">
-        <v>-27.1781369658821</v>
+        <v>-23.56966320913604</v>
       </c>
       <c r="F52">
-        <v>2.956815050307785</v>
+        <v>3.723215601173471</v>
       </c>
       <c r="G52">
-        <v>-5.784562817208789</v>
+        <v>-5.224579702209275</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.16463613786516</v>
       </c>
       <c r="E53">
-        <v>-25.84140389440193</v>
+        <v>-23.8042562766294</v>
       </c>
       <c r="F53">
-        <v>2.775506963387446</v>
+        <v>3.388021701835068</v>
       </c>
       <c r="G53">
-        <v>-6.485543303839201</v>
+        <v>-4.990425169284181</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.18261094425706</v>
       </c>
       <c r="E54">
-        <v>-25.54415938901245</v>
+        <v>-22.04273422933372</v>
       </c>
       <c r="F54">
-        <v>2.574704078009623</v>
+        <v>3.331041621666101</v>
       </c>
       <c r="G54">
-        <v>-7.030144052168038</v>
+        <v>-5.090778049458239</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.19710513334802</v>
       </c>
       <c r="E55">
-        <v>-26.08523504887093</v>
+        <v>-23.60762087826834</v>
       </c>
       <c r="F55">
-        <v>2.696691118480684</v>
+        <v>2.96906660419519</v>
       </c>
       <c r="G55">
-        <v>-6.411810974176919</v>
+        <v>-6.397442504968111</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.21249777939977</v>
       </c>
       <c r="E56">
-        <v>-25.40933766085609</v>
+        <v>-21.47839579849784</v>
       </c>
       <c r="F56">
-        <v>3.011889885450313</v>
+        <v>3.135177462743769</v>
       </c>
       <c r="G56">
-        <v>-6.898199570819647</v>
+        <v>-4.804714591462729</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.22333401118598</v>
       </c>
       <c r="E57">
-        <v>-24.86948921745369</v>
+        <v>-21.57453530168068</v>
       </c>
       <c r="F57">
-        <v>2.686767276995146</v>
+        <v>2.82597938924002</v>
       </c>
       <c r="G57">
-        <v>-7.138161865904958</v>
+        <v>-5.775257272866203</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.22840612077148</v>
       </c>
       <c r="E58">
-        <v>-23.83218790430871</v>
+        <v>-21.55183858995424</v>
       </c>
       <c r="F58">
-        <v>2.872309978078596</v>
+        <v>2.575273994782749</v>
       </c>
       <c r="G58">
-        <v>-7.266999030436555</v>
+        <v>-5.457484089720221</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.23102823035998</v>
       </c>
       <c r="E59">
-        <v>-23.76078745462977</v>
+        <v>-19.46053495152398</v>
       </c>
       <c r="F59">
-        <v>2.835132849040954</v>
+        <v>3.317083630928929</v>
       </c>
       <c r="G59">
-        <v>-7.532590947122689</v>
+        <v>-5.766991875757962</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.22587879465002</v>
       </c>
       <c r="E60">
-        <v>-23.45054170036427</v>
+        <v>-21.94343837976753</v>
       </c>
       <c r="F60">
-        <v>2.576773339781816</v>
+        <v>2.803828844889161</v>
       </c>
       <c r="G60">
-        <v>-7.578298363445753</v>
+        <v>-5.773669161631433</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.21405274793954</v>
       </c>
       <c r="E61">
-        <v>-23.63678877935174</v>
+        <v>-20.85803561571307</v>
       </c>
       <c r="F61">
-        <v>2.321997347907189</v>
+        <v>2.798991179256812</v>
       </c>
       <c r="G61">
-        <v>-8.178187695051234</v>
+        <v>-5.031522469316227</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.19418113086955</v>
       </c>
       <c r="E62">
-        <v>-22.5649759657943</v>
+        <v>-18.85709314763186</v>
       </c>
       <c r="F62">
-        <v>2.630999926703878</v>
+        <v>2.745349419721127</v>
       </c>
       <c r="G62">
-        <v>-7.340432768936927</v>
+        <v>-5.980871740667247</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.16345328498533</v>
       </c>
       <c r="E63">
-        <v>-22.64364461625555</v>
+        <v>-19.37308558996185</v>
       </c>
       <c r="F63">
-        <v>2.366091344758207</v>
+        <v>2.488073415024851</v>
       </c>
       <c r="G63">
-        <v>-7.805053741754299</v>
+        <v>-7.685814150284078</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.12488415356554</v>
       </c>
       <c r="E64">
-        <v>-21.80697734402039</v>
+        <v>-18.70549342327708</v>
       </c>
       <c r="F64">
-        <v>2.246099012993087</v>
+        <v>2.639961205267363</v>
       </c>
       <c r="G64">
-        <v>-7.517106862583669</v>
+        <v>-7.058782553938872</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.0734930710012</v>
       </c>
       <c r="E65">
-        <v>-21.31832782774871</v>
+        <v>-18.29597446181543</v>
       </c>
       <c r="F65">
-        <v>2.059081817932654</v>
+        <v>2.414188012899552</v>
       </c>
       <c r="G65">
-        <v>-7.979526135734653</v>
+        <v>-7.149564110824028</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.00704968790721</v>
       </c>
       <c r="E66">
-        <v>-22.06277725529167</v>
+        <v>-19.84972559316519</v>
       </c>
       <c r="F66">
-        <v>2.142218427212418</v>
+        <v>2.312320359907686</v>
       </c>
       <c r="G66">
-        <v>-8.601829491812699</v>
+        <v>-6.525689049619007</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.92927192528248</v>
       </c>
       <c r="E67">
-        <v>-22.37265620316254</v>
+        <v>-19.7194323390165</v>
       </c>
       <c r="F67">
-        <v>2.035272882041391</v>
+        <v>2.055238193183664</v>
       </c>
       <c r="G67">
-        <v>-9.27085744289724</v>
+        <v>-7.567050335939976</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.83475677732684</v>
       </c>
       <c r="E68">
-        <v>-21.35914296397985</v>
+        <v>-16.6927588088799</v>
       </c>
       <c r="F68">
-        <v>1.614934410838838</v>
+        <v>2.096543905356859</v>
       </c>
       <c r="G68">
-        <v>-8.846559401823884</v>
+        <v>-6.826212851026989</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.72405783500865</v>
       </c>
       <c r="E69">
-        <v>-21.00556424193496</v>
+        <v>-18.71427413437795</v>
       </c>
       <c r="F69">
-        <v>1.587951171060046</v>
+        <v>2.575474459694227</v>
       </c>
       <c r="G69">
-        <v>-9.491988807452897</v>
+        <v>-6.843810042250292</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.59697808375969</v>
       </c>
       <c r="E70">
-        <v>-21.22022749532055</v>
+        <v>-17.2338480541604</v>
       </c>
       <c r="F70">
-        <v>1.653524734665655</v>
+        <v>2.102615838419379</v>
       </c>
       <c r="G70">
-        <v>-8.414002526085406</v>
+        <v>-7.638508779061564</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.45179879744833</v>
       </c>
       <c r="E71">
-        <v>-21.26806629473758</v>
+        <v>-17.48549988324065</v>
       </c>
       <c r="F71">
-        <v>1.517702301833037</v>
+        <v>1.945481169047536</v>
       </c>
       <c r="G71">
-        <v>-8.978034668489274</v>
+        <v>-7.083473746173693</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.29366786964105</v>
       </c>
       <c r="E72">
-        <v>-20.7792990381417</v>
+        <v>-16.04834790064039</v>
       </c>
       <c r="F72">
-        <v>1.465278242379468</v>
+        <v>2.169690403758861</v>
       </c>
       <c r="G72">
-        <v>-9.042510672132362</v>
+        <v>-8.703258612658255</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.12120995230363</v>
       </c>
       <c r="E73">
-        <v>-21.34126454859756</v>
+        <v>-18.54618170768724</v>
       </c>
       <c r="F73">
-        <v>1.239993786779308</v>
+        <v>1.48883535458028</v>
       </c>
       <c r="G73">
-        <v>-9.085914670920697</v>
+        <v>-7.107472600659471</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.935337383760473</v>
       </c>
       <c r="E74">
-        <v>-20.71605437015058</v>
+        <v>-17.0089096932514</v>
       </c>
       <c r="F74">
-        <v>1.335378636476866</v>
+        <v>1.718506843945665</v>
       </c>
       <c r="G74">
-        <v>-8.664143170448115</v>
+        <v>-6.440078697911535</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.745455627963251</v>
       </c>
       <c r="E75">
-        <v>-20.78395430942159</v>
+        <v>-18.75358128876453</v>
       </c>
       <c r="F75">
-        <v>0.9052223548163332</v>
+        <v>1.49793414213263</v>
       </c>
       <c r="G75">
-        <v>-9.103485612371525</v>
+        <v>-6.915878792581935</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.552042852255905</v>
       </c>
       <c r="E76">
-        <v>-21.22766777811515</v>
+        <v>-18.13388226318488</v>
       </c>
       <c r="F76">
-        <v>0.9475933474695279</v>
+        <v>0.9886538628914938</v>
       </c>
       <c r="G76">
-        <v>-8.215206436684889</v>
+        <v>-7.653293963408421</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.362043118990012</v>
       </c>
       <c r="E77">
-        <v>-21.12831758686087</v>
+        <v>-17.5185351011266</v>
       </c>
       <c r="F77">
-        <v>0.702137317243798</v>
+        <v>1.506375205967157</v>
       </c>
       <c r="G77">
-        <v>-7.728529092544929</v>
+        <v>-6.680510207679847</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.180386621689152</v>
       </c>
       <c r="E78">
-        <v>-21.68590406295132</v>
+        <v>-18.32127504609629</v>
       </c>
       <c r="F78">
-        <v>0.8059408648560068</v>
+        <v>0.7618534949442115</v>
       </c>
       <c r="G78">
-        <v>-8.652777018966198</v>
+        <v>-7.39909444797668</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.010063728602876</v>
       </c>
       <c r="E79">
-        <v>-22.04612152789146</v>
+        <v>-19.89409105301833</v>
       </c>
       <c r="F79">
-        <v>0.5945232795787114</v>
+        <v>1.144623847695001</v>
       </c>
       <c r="G79">
-        <v>-7.62009784489152</v>
+        <v>-8.05097801641312</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.858989273294785</v>
       </c>
       <c r="E80">
-        <v>-22.46347474938637</v>
+        <v>-19.40467169616535</v>
       </c>
       <c r="F80">
-        <v>0.7383676223400399</v>
+        <v>0.906768088389957</v>
       </c>
       <c r="G80">
-        <v>-8.119496485017446</v>
+        <v>-5.885201163658517</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.726746744686563</v>
       </c>
       <c r="E81">
-        <v>-22.73856143145631</v>
+        <v>-19.82992710480365</v>
       </c>
       <c r="F81">
-        <v>0.4777706927259407</v>
+        <v>1.175135932609719</v>
       </c>
       <c r="G81">
-        <v>-7.902883362549144</v>
+        <v>-6.27654917783193</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.612566242720312</v>
       </c>
       <c r="E82">
-        <v>-22.38098406686265</v>
+        <v>-20.75514415778479</v>
       </c>
       <c r="F82">
-        <v>0.5585547385817541</v>
+        <v>0.4933108652024594</v>
       </c>
       <c r="G82">
-        <v>-8.052267536485983</v>
+        <v>-5.917655726102986</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.520885839714165</v>
       </c>
       <c r="E83">
-        <v>-23.51785746648829</v>
+        <v>-21.73247941812021</v>
       </c>
       <c r="F83">
-        <v>0.7230527657970827</v>
+        <v>0.9868977239975588</v>
       </c>
       <c r="G83">
-        <v>-7.837249087695571</v>
+        <v>-7.109027899678648</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.445934817230563</v>
       </c>
       <c r="E84">
-        <v>-25.25821342627212</v>
+        <v>-21.97918162511007</v>
       </c>
       <c r="F84">
-        <v>0.6226248153512819</v>
+        <v>0.9872340411630954</v>
       </c>
       <c r="G84">
-        <v>-6.936921266442654</v>
+        <v>-6.509552001989658</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.386638368077524</v>
       </c>
       <c r="E85">
-        <v>-25.58030566854168</v>
+        <v>-22.20344977186594</v>
       </c>
       <c r="F85">
-        <v>0.5250025452987629</v>
+        <v>0.6438798945397144</v>
       </c>
       <c r="G85">
-        <v>-7.475241756706714</v>
+        <v>-6.591992693670707</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.337544687598996</v>
       </c>
       <c r="E86">
-        <v>-26.46301393601282</v>
+        <v>-23.54479735835992</v>
       </c>
       <c r="F86">
-        <v>0.4576910668820807</v>
+        <v>0.8400281834812064</v>
       </c>
       <c r="G86">
-        <v>-6.920442971771123</v>
+        <v>-5.913009516374812</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.292961936002488</v>
       </c>
       <c r="E87">
-        <v>-27.94122106396661</v>
+        <v>-25.86212619146103</v>
       </c>
       <c r="F87">
-        <v>0.7314126496261353</v>
+        <v>0.7774036078295639</v>
       </c>
       <c r="G87">
-        <v>-6.826573785398528</v>
+        <v>-5.045136257566362</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.252162922653696</v>
       </c>
       <c r="E88">
-        <v>-28.82179189170613</v>
+        <v>-25.36629904388719</v>
       </c>
       <c r="F88">
-        <v>0.4298148470430717</v>
+        <v>-0.03511712655438719</v>
       </c>
       <c r="G88">
-        <v>-6.645076296059403</v>
+        <v>-5.044578449901257</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.208930569190946</v>
       </c>
       <c r="E89">
-        <v>-30.03778678919379</v>
+        <v>-27.91607444780202</v>
       </c>
       <c r="F89">
-        <v>0.7331257134151247</v>
+        <v>0.3601806264289397</v>
       </c>
       <c r="G89">
-        <v>-7.014423719676739</v>
+        <v>-4.898705183033023</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.159718704826359</v>
       </c>
       <c r="E90">
-        <v>-31.08588851284707</v>
+        <v>-29.08160855942221</v>
       </c>
       <c r="F90">
-        <v>-0.0409687138877629</v>
+        <v>0.733281446486851</v>
       </c>
       <c r="G90">
-        <v>-6.476795567161721</v>
+        <v>-5.448916820228511</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.107377044534587</v>
       </c>
       <c r="E91">
-        <v>-32.37047620612891</v>
+        <v>-31.2029812652634</v>
       </c>
       <c r="F91">
-        <v>0.2142686786302236</v>
+        <v>0.8498575910828254</v>
       </c>
       <c r="G91">
-        <v>-6.880540036386716</v>
+        <v>-5.386803296108222</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.048490984906747</v>
       </c>
       <c r="E92">
-        <v>-33.85389560766554</v>
+        <v>-33.3166238659735</v>
       </c>
       <c r="F92">
-        <v>0.5315996632946581</v>
+        <v>-0.04485375700689258</v>
       </c>
       <c r="G92">
-        <v>-6.300292097036071</v>
+        <v>-5.455567856329504</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.9856800487701</v>
       </c>
       <c r="E93">
-        <v>-35.52603010652381</v>
+        <v>-33.47512272047897</v>
       </c>
       <c r="F93">
-        <v>0.4550510599693587</v>
+        <v>0.1877236452075134</v>
       </c>
       <c r="G93">
-        <v>-6.053875639143333</v>
+        <v>-4.253646555440227</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.917685828335364</v>
       </c>
       <c r="E94">
-        <v>-38.13092836029701</v>
+        <v>-35.02054145965461</v>
       </c>
       <c r="F94">
-        <v>0.400123674224529</v>
+        <v>-0.4276870656802953</v>
       </c>
       <c r="G94">
-        <v>-6.162142825718771</v>
+        <v>-4.613737653038369</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.844545292679738</v>
       </c>
       <c r="E95">
-        <v>-39.54045438721347</v>
+        <v>-37.17596602579648</v>
       </c>
       <c r="F95">
-        <v>0.5082662102926017</v>
+        <v>-0.0880473184910672</v>
       </c>
       <c r="G95">
-        <v>-6.019176721152204</v>
+        <v>-4.923150283650886</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.769936448322334</v>
       </c>
       <c r="E96">
-        <v>-41.75313697870832</v>
+        <v>-38.34835171859027</v>
       </c>
       <c r="F96">
-        <v>0.4563441414851287</v>
+        <v>-0.4933211001063085</v>
       </c>
       <c r="G96">
-        <v>-6.09472684755842</v>
+        <v>-5.310849579450196</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.691342443760193</v>
       </c>
       <c r="E97">
-        <v>-42.99008286119247</v>
+        <v>-42.73371236219623</v>
       </c>
       <c r="F97">
-        <v>0.5433541967403832</v>
+        <v>-0.2105322077712105</v>
       </c>
       <c r="G97">
-        <v>-6.292354822083775</v>
+        <v>-4.445515986128757</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.607411793937457</v>
       </c>
       <c r="E98">
-        <v>-45.18108085490159</v>
+        <v>-42.46443344804112</v>
       </c>
       <c r="F98">
-        <v>0.4287984402398367</v>
+        <v>0.07410642897433882</v>
       </c>
       <c r="G98">
-        <v>-6.594171424786178</v>
+        <v>-5.080035330072617</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.521207949667615</v>
       </c>
       <c r="E99">
-        <v>-46.41950981262325</v>
+        <v>-43.52582850714392</v>
       </c>
       <c r="F99">
-        <v>0.3006102413914188</v>
+        <v>-0.03518173921180556</v>
       </c>
       <c r="G99">
-        <v>-6.976663421970648</v>
+        <v>-5.111968178289133</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.429753109049461</v>
       </c>
       <c r="E100">
-        <v>-49.24851884868055</v>
+        <v>-44.98204989379047</v>
       </c>
       <c r="F100">
-        <v>0.5484047527952518</v>
+        <v>-0.8780853331956369</v>
       </c>
       <c r="G100">
-        <v>-7.345121634545374</v>
+        <v>-6.171586181366853</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.333435010921407</v>
       </c>
       <c r="E101">
-        <v>-50.6262798946702</v>
+        <v>-49.31584027539708</v>
       </c>
       <c r="F101">
-        <v>0.3344647887764318</v>
+        <v>-0.8876728575156384</v>
       </c>
       <c r="G101">
-        <v>-7.090800713915933</v>
+        <v>-5.275642072117354</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.233086022971903</v>
       </c>
       <c r="E102">
-        <v>-52.5134489817827</v>
+        <v>-52.04383603812077</v>
       </c>
       <c r="F102">
-        <v>0.3881032348425054</v>
+        <v>-0.8291967458172157</v>
       </c>
       <c r="G102">
-        <v>-7.194372472439805</v>
+        <v>-5.948407334558101</v>
       </c>
     </row>
   </sheetData>
